--- a/k4t2w_11111/apps/abc/k4t2_app_11111.xlsx
+++ b/k4t2w_11111/apps/abc/k4t2_app_11111.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\自用\MY\Powershell群\pshell\字符界面脚本\k4t=国产k8s\git未来文件\m\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A649E9-C06F-40AB-A112-B5B56C29CC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1224A7DC-ECA3-4347-BD05-703013C6708F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16284" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="127">
   <si>
     <t>帮助页面</t>
   </si>
@@ -422,6 +422,46 @@
   </si>
   <si>
     <t>2 不要更改,config页面中,字段名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本应用依赖的所有应用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>all=默认绑定组内所有worker。若更改组内worker后，默认更改。None=默认绑定为空，应手动绑定。若更改组内worker后，应手动添加删除这里的绑定。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应用绑定worker的策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应用绑定worker组的策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锁定副本端口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锁定副本ip端口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32769---65000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -988,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F934616-16B2-4028-8234-B920F293C7EE}">
-  <dimension ref="B2:K73"/>
+  <dimension ref="B2:K77"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
@@ -1200,34 +1240,33 @@
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I16" s="10"/>
+        <v>117</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I17" s="10"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="I17" s="10"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="4">
-        <v>0</v>
       </c>
       <c r="I18" s="10"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F19" s="4">
         <v>0</v>
@@ -1236,394 +1275,470 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+      <c r="I20" s="10"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="22">
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="22">
         <v>0</v>
       </c>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="16" t="s">
+      <c r="I21" s="10"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="10"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="16" t="s">
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13" t="s">
         <v>30</v>
-      </c>
-      <c r="I22" s="10"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="I23" s="10"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="4">
-        <v>10</v>
+        <v>95</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13" t="s">
+        <v>31</v>
       </c>
       <c r="I24" s="10"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" s="4">
-        <v>20</v>
+      <c r="B25" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="I25" s="10"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="E26" s="20"/>
-      <c r="F26" s="22"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13" t="b">
+        <v>0</v>
+      </c>
       <c r="I26" s="10"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="22"/>
+        <v>32</v>
+      </c>
+      <c r="F27" s="4">
+        <v>10</v>
+      </c>
       <c r="I27" s="10"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="25" t="s">
-        <v>97</v>
+      <c r="B28" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="F28" s="4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I28" s="10"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="20"/>
+      <c r="F29" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="I29" s="10"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I30" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="D30" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" s="20"/>
+      <c r="F30" s="22"/>
+      <c r="I30" s="10" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="25" t="s">
-        <v>35</v>
+        <v>97</v>
+      </c>
+      <c r="F31" s="4">
+        <v>0</v>
       </c>
       <c r="I31" s="10"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F32" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>70</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I32" s="10"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" s="4">
-        <v>300</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>68</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I33" s="10"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F34" s="4">
-        <v>1000</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>66</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="I34" s="10"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>37</v>
+        <v>98</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="22"/>
-      <c r="I36" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>40</v>
+      <c r="B36" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F36" s="4">
+        <v>300</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="I37" s="10"/>
+        <v>100</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B39" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="22"/>
+      <c r="I39" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I40" s="10"/>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B41" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F41" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I38" s="10" t="s">
+      <c r="I41" s="10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" s="16" t="s">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F42" s="4">
         <v>6</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="I42" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B40" s="16" t="s">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B43" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F43" s="4">
         <v>6</v>
       </c>
-      <c r="I40" s="10" t="s">
+      <c r="I43" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B41" s="16" t="s">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F44" s="4">
         <v>6</v>
       </c>
-      <c r="I41" s="10" t="s">
+      <c r="I44" s="10" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B42" s="11" t="s">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B45" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20" t="s">
+      <c r="C45" s="20"/>
+      <c r="D45" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="20"/>
-      <c r="F42" s="4" t="s">
+      <c r="E45" s="20"/>
+      <c r="F45" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="I42" s="22" t="s">
+      <c r="I45" s="22" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B43" s="11" t="s">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20" t="s">
+      <c r="C46" s="20"/>
+      <c r="D46" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E43" s="20"/>
-      <c r="F43" s="4" t="s">
+      <c r="E46" s="20"/>
+      <c r="F46" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="I43" s="22" t="s">
+      <c r="I46" s="22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B44" s="11" t="s">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B47" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11" t="s">
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I47" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B45" s="26" t="s">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F48" s="4">
         <v>120</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I48" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B46" s="26" t="s">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B49" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F49" s="4">
         <v>300</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G49" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="I49" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="23" t="s">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B50" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F50" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I47" s="10"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="24" t="s">
+      <c r="I50" s="10"/>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B51" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B52" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F52" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B69" s="18"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="18"/>
-    </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B70" s="3" t="s">
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B53" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="18"/>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B74" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D74" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F74" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G74" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="H74" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I70" s="3" t="s">
+      <c r="I74" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B71" s="26" t="s">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B75" s="26" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B72" s="16" t="s">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B73" s="23" t="s">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B77" s="23" t="s">
         <v>104</v>
       </c>
     </row>

--- a/k4t2w_11111/apps/abc/k4t2_app_11111.xlsx
+++ b/k4t2w_11111/apps/abc/k4t2_app_11111.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\自用\MY\Powershell群\pshell\字符界面脚本\k4t=国产k8s\git未来文件\m\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1224A7DC-ECA3-4347-BD05-703013C6708F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB208D3-2A1E-41DB-9755-3760899118E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16284" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="31196" windowHeight="16421" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="config" sheetId="2" r:id="rId2"/>
+    <sheet name="workers" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="145">
   <si>
     <t>帮助页面</t>
   </si>
@@ -218,9 +222,6 @@
     <t>空</t>
   </si>
   <si>
-    <t>已经绑定的woker组</t>
-  </si>
-  <si>
     <t>end</t>
   </si>
   <si>
@@ -462,6 +463,97 @@
   </si>
   <si>
     <t>32769---65000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对标k8 daemonset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用于建立redis 集群，mysql集群。具体看教程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kata虚拟机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用kata-container虚拟机启动容器（本质是qemu虚拟机）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>worker优先级</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>worker权重百分比</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>192.168.2.11</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>192.168.2.12</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1为最优先，999为最低优先。
+适用算法【按节点优先级_让铲屎官填满cpu内存之一】</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>适用算法【使用节点权重百分比】。
+所有节点的百分比和，应该大于99，小于等于100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>4 禁止你使用config，workers，workersold1，workersold2，workersold3名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enable</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经启用</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>worker</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>weight percentage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>在wg目录下，在应用app的那一时刻，会把文件内容复制到【本文件的worker页】
+Excel文件支持多个app公用，但修改此文件，将导致所有引用此worker文件的app变更，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>慎用文件公用</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>priority</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经绑定的wg组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经绑定的mwg组</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -469,7 +561,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -498,8 +590,37 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -524,8 +645,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -591,13 +718,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -678,6 +820,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -993,30 +1165,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A78C0F-F395-43A5-A0EF-42BC4EAEA1D1}">
-  <dimension ref="B2:B5"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:B6"/>
+  <sheetFormatPr defaultRowHeight="13.95" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="89.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="22.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:2" ht="23" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="22.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:2" ht="23" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="23" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="22.2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" ht="22.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:2" ht="23" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="23" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1028,8 +1205,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F934616-16B2-4028-8234-B920F293C7EE}">
-  <dimension ref="B2:K77"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:K78"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
     <col min="2" max="2" width="40.88671875" style="3" customWidth="1"/>
@@ -1085,7 +1262,7 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>14</v>
@@ -1103,7 +1280,7 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>17</v>
@@ -1113,7 +1290,7 @@
       </c>
       <c r="I5" s="10"/>
     </row>
-    <row r="6" spans="2:9" ht="93.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="94.4" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>19</v>
       </c>
@@ -1131,32 +1308,32 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F7" s="4">
         <v>3</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>85</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -1165,15 +1342,15 @@
         <v>2</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F10" s="4" t="b">
         <v>1</v>
@@ -1185,13 +1362,13 @@
         <v>22</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I11" s="10"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
@@ -1202,12 +1379,12 @@
       <c r="G12" s="22"/>
       <c r="H12" s="22"/>
       <c r="I12" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F13" s="4">
         <v>2</v>
@@ -1218,7 +1395,7 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F14" s="4">
         <v>5</v>
@@ -1229,10 +1406,10 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>24</v>
@@ -1240,7 +1417,7 @@
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>24</v>
@@ -1251,7 +1428,7 @@
         <v>25</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I17" s="10"/>
     </row>
@@ -1260,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I18" s="10"/>
     </row>
@@ -1284,7 +1461,7 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="20"/>
@@ -1296,7 +1473,7 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -1308,7 +1485,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -1320,7 +1497,7 @@
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -1332,10 +1509,10 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F25" s="4" t="b">
         <v>0</v>
@@ -1344,17 +1521,19 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I26" s="10"/>
+      <c r="I26" s="10" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="13" t="s">
@@ -1367,7 +1546,7 @@
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F28" s="4">
         <v>20</v>
@@ -1376,208 +1555,210 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E29" s="20"/>
       <c r="F29" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I29" s="10"/>
+      <c r="I29" s="10" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E30" s="20"/>
       <c r="F30" s="22"/>
       <c r="I30" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="F31" s="4">
+        <v>128</v>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="D31" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="20"/>
+      <c r="F31" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I31" s="10"/>
+      <c r="I31" s="10" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>73</v>
+        <v>96</v>
+      </c>
+      <c r="F32" s="4">
+        <v>0</v>
       </c>
       <c r="I32" s="10"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I33" s="10"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="25" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="I34" s="10"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F35" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>70</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="I35" s="10"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F36" s="4">
-        <v>300</v>
+        <v>0.5</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F37" s="4">
-        <v>1000</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>66</v>
+        <v>300</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F38" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B39" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="F38" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="I38" s="3" t="s">
+      <c r="F39" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" s="13" t="s">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="22"/>
-      <c r="I39" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J39" s="3" t="s">
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="22"/>
+      <c r="I40" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="K40" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B40" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="I40" s="10"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I41" s="10"/>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F42" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I41" s="10" t="s">
+      <c r="I42" s="10" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B42" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="F42" s="4">
-        <v>6</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F43" s="4">
         <v>6</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F44" s="4">
         <v>6</v>
       </c>
       <c r="I44" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B45" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F45" s="4">
+        <v>6</v>
+      </c>
+      <c r="I45" s="10" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B45" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E45" s="20"/>
-      <c r="F45" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I45" s="22" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="11" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="20" t="s">
@@ -1585,161 +1766,183 @@
       </c>
       <c r="E46" s="20"/>
       <c r="F46" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E47" s="20"/>
+      <c r="F47" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I47" s="22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11" t="s">
+      <c r="I48" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F48" s="4">
-        <v>120</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49" s="26" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F49" s="4">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>52</v>
       </c>
       <c r="I49" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B50" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F50" s="4">
+        <v>300</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B50" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F50" s="4" t="s">
+    <row r="51" spans="2:9" ht="62.95" x14ac:dyDescent="0.25">
+      <c r="B51" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="I50" s="10"/>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B51" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>120</v>
+      <c r="I51" s="34" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52" s="24" t="s">
-        <v>59</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C52" s="16"/>
       <c r="D52" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B53" s="24" t="s">
-        <v>122</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="C53" s="16"/>
       <c r="D53" s="3" t="s">
-        <v>118</v>
+        <v>57</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B73" s="18"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="18"/>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B54" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" s="16"/>
+      <c r="D54" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B74" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="19"/>
+      <c r="H74" s="19"/>
+      <c r="I74" s="18"/>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B75" s="26" t="s">
+      <c r="B75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B76" s="26" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B77" s="16" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B76" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B77" s="23" t="s">
-        <v>104</v>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B78" s="23" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1747,4 +1950,674 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F81CDE4-8532-42F5-811F-D967A61B49A7}">
+  <dimension ref="B2:G104"/>
+  <sheetFormatPr defaultRowHeight="13.95" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="33"/>
+    <col min="2" max="3" width="28.6640625" style="33" customWidth="1"/>
+    <col min="4" max="4" width="49.88671875" style="33" customWidth="1"/>
+    <col min="5" max="5" width="49.109375" style="33" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="33"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="76.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="21.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B4" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="35"/>
+      <c r="G4" s="36"/>
+    </row>
+    <row r="5" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B5" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31">
+        <v>1</v>
+      </c>
+      <c r="E5" s="31">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B6" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31">
+        <v>2</v>
+      </c>
+      <c r="E6" s="31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+    </row>
+    <row r="8" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+    </row>
+    <row r="9" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+    </row>
+    <row r="10" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+    </row>
+    <row r="11" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+    </row>
+    <row r="12" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+    </row>
+    <row r="13" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+    </row>
+    <row r="14" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+    </row>
+    <row r="15" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+    </row>
+    <row r="16" spans="2:7" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+    </row>
+    <row r="17" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+    </row>
+    <row r="18" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+    </row>
+    <row r="19" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+    </row>
+    <row r="20" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+    </row>
+    <row r="21" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+    </row>
+    <row r="22" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+    </row>
+    <row r="23" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+    </row>
+    <row r="24" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+    </row>
+    <row r="25" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+    </row>
+    <row r="26" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+    </row>
+    <row r="27" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+    </row>
+    <row r="28" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+    </row>
+    <row r="29" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+    </row>
+    <row r="30" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+    </row>
+    <row r="31" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+    </row>
+    <row r="32" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+    </row>
+    <row r="33" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+    </row>
+    <row r="34" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+    </row>
+    <row r="35" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+    </row>
+    <row r="36" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+    </row>
+    <row r="37" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+    </row>
+    <row r="38" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+    </row>
+    <row r="39" spans="2:5" ht="20.6" x14ac:dyDescent="0.25">
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="32"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" s="32"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" s="32"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B65" s="32"/>
+      <c r="C65" s="32"/>
+      <c r="D65" s="32"/>
+      <c r="E65" s="32"/>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B66" s="32"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="32"/>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B67" s="32"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B68" s="32"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B69" s="32"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B72" s="32"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="32"/>
+      <c r="E72" s="32"/>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B73" s="32"/>
+      <c r="C73" s="32"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="32"/>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B74" s="32"/>
+      <c r="C74" s="32"/>
+      <c r="D74" s="32"/>
+      <c r="E74" s="32"/>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B75" s="32"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="32"/>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B76" s="32"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
+      <c r="E76" s="32"/>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B77" s="32"/>
+      <c r="C77" s="32"/>
+      <c r="D77" s="32"/>
+      <c r="E77" s="32"/>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B78" s="32"/>
+      <c r="C78" s="32"/>
+      <c r="D78" s="32"/>
+      <c r="E78" s="32"/>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B79" s="32"/>
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B80" s="32"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="32"/>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B81" s="32"/>
+      <c r="C81" s="32"/>
+      <c r="D81" s="32"/>
+      <c r="E81" s="32"/>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B82" s="32"/>
+      <c r="C82" s="32"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="32"/>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B83" s="32"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="32"/>
+      <c r="E83" s="32"/>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B84" s="32"/>
+      <c r="C84" s="32"/>
+      <c r="D84" s="32"/>
+      <c r="E84" s="32"/>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B85" s="32"/>
+      <c r="C85" s="32"/>
+      <c r="D85" s="32"/>
+      <c r="E85" s="32"/>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B86" s="32"/>
+      <c r="C86" s="32"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="32"/>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B87" s="32"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B88" s="32"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B89" s="32"/>
+      <c r="C89" s="32"/>
+      <c r="D89" s="32"/>
+      <c r="E89" s="32"/>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B90" s="32"/>
+      <c r="C90" s="32"/>
+      <c r="D90" s="32"/>
+      <c r="E90" s="32"/>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B91" s="32"/>
+      <c r="C91" s="32"/>
+      <c r="D91" s="32"/>
+      <c r="E91" s="32"/>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B92" s="32"/>
+      <c r="C92" s="32"/>
+      <c r="D92" s="32"/>
+      <c r="E92" s="32"/>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B93" s="32"/>
+      <c r="C93" s="32"/>
+      <c r="D93" s="32"/>
+      <c r="E93" s="32"/>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B94" s="32"/>
+      <c r="C94" s="32"/>
+      <c r="D94" s="32"/>
+      <c r="E94" s="32"/>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B95" s="32"/>
+      <c r="C95" s="32"/>
+      <c r="D95" s="32"/>
+      <c r="E95" s="32"/>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B96" s="32"/>
+      <c r="C96" s="32"/>
+      <c r="D96" s="32"/>
+      <c r="E96" s="32"/>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B97" s="32"/>
+      <c r="C97" s="32"/>
+      <c r="D97" s="32"/>
+      <c r="E97" s="32"/>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B98" s="32"/>
+      <c r="C98" s="32"/>
+      <c r="D98" s="32"/>
+      <c r="E98" s="32"/>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B99" s="32"/>
+      <c r="C99" s="32"/>
+      <c r="D99" s="32"/>
+      <c r="E99" s="32"/>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B100" s="32"/>
+      <c r="C100" s="32"/>
+      <c r="D100" s="32"/>
+      <c r="E100" s="32"/>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B101" s="32"/>
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
+      <c r="E101" s="32"/>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B102" s="32"/>
+      <c r="C102" s="32"/>
+      <c r="D102" s="32"/>
+      <c r="E102" s="32"/>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B103" s="32"/>
+      <c r="C103" s="32"/>
+      <c r="D103" s="32"/>
+      <c r="E103" s="32"/>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B104" s="32"/>
+      <c r="C104" s="32"/>
+      <c r="D104" s="32"/>
+      <c r="E104" s="32"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>